--- a/缓存数据/ds_csm_8_Part.xlsx
+++ b/缓存数据/ds_csm_8_Part.xlsx
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14468.87</v>
+        <v>11113.79</v>
       </c>
       <c r="C2" t="n">
-        <v>11113.79</v>
+        <v>10659.08</v>
       </c>
       <c r="D2" t="n">
-        <v>10659.08</v>
+        <v>8241.189999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8241.190000000001</v>
+        <v>7745.010000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>7745.010000000002</v>
+        <v>11174.38</v>
       </c>
       <c r="G2" t="n">
-        <v>11174.38</v>
+        <v>11730.84</v>
       </c>
       <c r="H2" t="n">
-        <v>11730.84</v>
+        <v>10873.39</v>
       </c>
       <c r="I2" t="n">
-        <v>10873.39</v>
+        <v>12209.82</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44919.22999999998</v>
+        <v>44297.19000000002</v>
       </c>
       <c r="C3" t="n">
-        <v>44297.19</v>
+        <v>42057.63000000003</v>
       </c>
       <c r="D3" t="n">
-        <v>42057.62999999998</v>
+        <v>29412.67000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>29412.67000000002</v>
+        <v>25123.42</v>
       </c>
       <c r="F3" t="n">
-        <v>25123.41999999999</v>
+        <v>44000.96999999997</v>
       </c>
       <c r="G3" t="n">
-        <v>44000.97000000001</v>
+        <v>45852.23000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>45852.23</v>
+        <v>43646.35000000003</v>
       </c>
       <c r="I3" t="n">
-        <v>43646.35</v>
+        <v>45311.98000000005</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>152369.7900000001</v>
+        <v>157074.69</v>
       </c>
       <c r="C4" t="n">
-        <v>157074.69</v>
+        <v>156166.4899999998</v>
       </c>
       <c r="D4" t="n">
-        <v>156166.4899999999</v>
+        <v>115699.7099999999</v>
       </c>
       <c r="E4" t="n">
-        <v>115699.7099999999</v>
+        <v>98614.65999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>98614.66</v>
+        <v>151531.67</v>
       </c>
       <c r="G4" t="n">
-        <v>151531.67</v>
+        <v>152537.6400000001</v>
       </c>
       <c r="H4" t="n">
-        <v>152537.6400000001</v>
+        <v>164254.83</v>
       </c>
       <c r="I4" t="n">
-        <v>164254.83</v>
+        <v>167150.3600000001</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57887.51</v>
+        <v>58343</v>
       </c>
       <c r="C5" t="n">
-        <v>58342.99999999999</v>
+        <v>57171.91999999998</v>
       </c>
       <c r="D5" t="n">
-        <v>57171.91999999999</v>
+        <v>49581.12</v>
       </c>
       <c r="E5" t="n">
-        <v>49581.12</v>
+        <v>46530.61999999998</v>
       </c>
       <c r="F5" t="n">
-        <v>46530.61999999998</v>
+        <v>60896.50000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>60896.50000000001</v>
+        <v>61136.78</v>
       </c>
       <c r="H5" t="n">
-        <v>61136.78</v>
+        <v>58779.22000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>58779.22000000002</v>
+        <v>65582.41</v>
       </c>
     </row>
     <row r="6">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2043.1</v>
+        <v>1850.44</v>
       </c>
       <c r="C7" t="n">
-        <v>1850.44</v>
+        <v>1292.96</v>
       </c>
       <c r="D7" t="n">
-        <v>1292.96</v>
+        <v>595.95</v>
       </c>
       <c r="E7" t="n">
-        <v>595.95</v>
+        <v>352.17</v>
       </c>
       <c r="F7" t="n">
-        <v>352.17</v>
+        <v>1737.299999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1737.3</v>
+        <v>2212.380000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2212.380000000001</v>
+        <v>2610.55</v>
       </c>
       <c r="I7" t="n">
-        <v>2610.55</v>
+        <v>2053.69</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13043.06</v>
+        <v>12806.09</v>
       </c>
       <c r="C8" t="n">
-        <v>12806.09</v>
+        <v>12826.92</v>
       </c>
       <c r="D8" t="n">
-        <v>12826.92</v>
+        <v>12633.54</v>
       </c>
       <c r="E8" t="n">
-        <v>12633.54</v>
+        <v>12619.59</v>
       </c>
       <c r="F8" t="n">
-        <v>12619.59</v>
+        <v>12576.22</v>
       </c>
       <c r="G8" t="n">
-        <v>12576.22</v>
+        <v>12701.36</v>
       </c>
       <c r="H8" t="n">
-        <v>12701.36</v>
+        <v>12644</v>
       </c>
       <c r="I8" t="n">
-        <v>12644</v>
+        <v>12457.37</v>
       </c>
     </row>
     <row r="9">
@@ -694,28 +694,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1320526.94</v>
+        <v>1378720.069999996</v>
       </c>
       <c r="C9" t="n">
-        <v>1378720.069999997</v>
+        <v>1362777.650000002</v>
       </c>
       <c r="D9" t="n">
-        <v>1362777.650000001</v>
+        <v>1361544.599999999</v>
       </c>
       <c r="E9" t="n">
-        <v>1361544.599999999</v>
+        <v>1445744.96</v>
       </c>
       <c r="F9" t="n">
-        <v>1445744.960000001</v>
+        <v>1544634.289999998</v>
       </c>
       <c r="G9" t="n">
-        <v>1544634.29</v>
+        <v>1461846.640000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1461846.640000001</v>
+        <v>1413893.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1413893.899999999</v>
+        <v>1457271.569999997</v>
       </c>
     </row>
     <row r="10">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10043.7</v>
+        <v>10345.54</v>
       </c>
       <c r="C10" t="n">
-        <v>10345.54000000001</v>
+        <v>10764.14</v>
       </c>
       <c r="D10" t="n">
-        <v>10764.14</v>
+        <v>9611.279999999995</v>
       </c>
       <c r="E10" t="n">
-        <v>9611.280000000001</v>
+        <v>8216.84</v>
       </c>
       <c r="F10" t="n">
-        <v>8216.84</v>
+        <v>10698.95</v>
       </c>
       <c r="G10" t="n">
-        <v>10698.95</v>
+        <v>10196.72000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>10196.72000000001</v>
+        <v>11209.40999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>11209.41</v>
+        <v>10664.34</v>
       </c>
     </row>
     <row r="11">
@@ -756,28 +756,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36521.75999999999</v>
+        <v>35022.91000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>35022.91</v>
+        <v>33172.77000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>33172.77000000001</v>
+        <v>32815.35999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>32815.35999999999</v>
+        <v>29344.50999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>29344.50999999999</v>
+        <v>35209.00000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>35209.00000000001</v>
+        <v>32545.99999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>32546</v>
+        <v>35247.49000000002</v>
       </c>
       <c r="I11" t="n">
-        <v>35247.49000000001</v>
+        <v>31165.14999999999</v>
       </c>
     </row>
     <row r="12">
@@ -787,28 +787,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>734145.2500000002</v>
+        <v>729122.6999999996</v>
       </c>
       <c r="C12" t="n">
-        <v>729122.6999999993</v>
+        <v>701875.6600000004</v>
       </c>
       <c r="D12" t="n">
-        <v>701875.6600000003</v>
+        <v>714332.6699999999</v>
       </c>
       <c r="E12" t="n">
-        <v>714332.6699999992</v>
+        <v>743788.97</v>
       </c>
       <c r="F12" t="n">
-        <v>743788.9700000003</v>
+        <v>726909.91</v>
       </c>
       <c r="G12" t="n">
-        <v>726909.9100000004</v>
+        <v>695111.05</v>
       </c>
       <c r="H12" t="n">
-        <v>695111.05</v>
+        <v>705491.62</v>
       </c>
       <c r="I12" t="n">
-        <v>705491.6200000001</v>
+        <v>727275.5199999989</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/ds_csm_8_Part.xlsx
+++ b/缓存数据/ds_csm_8_Part.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11113.79</v>
+        <v>17381.17</v>
       </c>
       <c r="C2" t="n">
-        <v>10659.08</v>
+        <v>22889.36</v>
       </c>
       <c r="D2" t="n">
-        <v>8241.189999999999</v>
+        <v>24616.15</v>
       </c>
       <c r="E2" t="n">
-        <v>7745.010000000001</v>
+        <v>11594.31</v>
       </c>
       <c r="F2" t="n">
-        <v>11174.38</v>
+        <v>9979.870000000004</v>
       </c>
       <c r="G2" t="n">
-        <v>11730.84</v>
+        <v>14990.03</v>
       </c>
       <c r="H2" t="n">
-        <v>10873.39</v>
+        <v>14554.65</v>
       </c>
       <c r="I2" t="n">
-        <v>12209.82</v>
+        <v>13378.44</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44297.19000000002</v>
+        <v>54588.80999999994</v>
       </c>
       <c r="C3" t="n">
-        <v>42057.63000000003</v>
+        <v>59124.66999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>29412.67000000001</v>
+        <v>54958.86000000004</v>
       </c>
       <c r="E3" t="n">
-        <v>25123.42</v>
+        <v>54116.52</v>
       </c>
       <c r="F3" t="n">
-        <v>44000.96999999997</v>
+        <v>26756.60999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>45852.23000000001</v>
+        <v>51068.73000000003</v>
       </c>
       <c r="H3" t="n">
-        <v>43646.35000000003</v>
+        <v>44899.20999999997</v>
       </c>
       <c r="I3" t="n">
-        <v>45311.98000000005</v>
+        <v>38701.26000000003</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>157074.69</v>
+        <v>170114.5999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>156166.4899999998</v>
+        <v>169965.87</v>
       </c>
       <c r="D4" t="n">
-        <v>115699.7099999999</v>
+        <v>153620.84</v>
       </c>
       <c r="E4" t="n">
-        <v>98614.65999999999</v>
+        <v>112949.82</v>
       </c>
       <c r="F4" t="n">
-        <v>151531.67</v>
+        <v>98365.75000000007</v>
       </c>
       <c r="G4" t="n">
-        <v>152537.6400000001</v>
+        <v>150241.26</v>
       </c>
       <c r="H4" t="n">
-        <v>164254.83</v>
+        <v>152051.22</v>
       </c>
       <c r="I4" t="n">
-        <v>167150.3600000001</v>
+        <v>157032.1699999999</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58343</v>
+        <v>372727.4899999996</v>
       </c>
       <c r="C5" t="n">
-        <v>57171.91999999998</v>
+        <v>1300027.3</v>
       </c>
       <c r="D5" t="n">
-        <v>49581.12</v>
+        <v>1408291.270000001</v>
       </c>
       <c r="E5" t="n">
-        <v>46530.61999999998</v>
+        <v>1256638.76</v>
       </c>
       <c r="F5" t="n">
-        <v>60896.50000000001</v>
+        <v>1248041.189999999</v>
       </c>
       <c r="G5" t="n">
-        <v>61136.78</v>
+        <v>62423.78</v>
       </c>
       <c r="H5" t="n">
-        <v>58779.22000000001</v>
+        <v>97498.47</v>
       </c>
       <c r="I5" t="n">
-        <v>65582.41</v>
+        <v>116166.18</v>
       </c>
     </row>
     <row r="6">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1850.44</v>
+        <v>3701.91</v>
       </c>
       <c r="C7" t="n">
-        <v>1292.96</v>
+        <v>4820.52</v>
       </c>
       <c r="D7" t="n">
-        <v>595.95</v>
+        <v>1453.08</v>
       </c>
       <c r="E7" t="n">
-        <v>352.17</v>
+        <v>4740.320000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1737.299999999999</v>
+        <v>1188.17</v>
       </c>
       <c r="G7" t="n">
-        <v>2212.380000000001</v>
+        <v>2748.23</v>
       </c>
       <c r="H7" t="n">
-        <v>2610.55</v>
+        <v>1628.56</v>
       </c>
       <c r="I7" t="n">
-        <v>2053.69</v>
+        <v>1005.52</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12806.09</v>
+        <v>15132.83</v>
       </c>
       <c r="C8" t="n">
-        <v>12826.92</v>
+        <v>15176.63</v>
       </c>
       <c r="D8" t="n">
-        <v>12633.54</v>
+        <v>15422.45</v>
       </c>
       <c r="E8" t="n">
-        <v>12619.59</v>
+        <v>15083.56</v>
       </c>
       <c r="F8" t="n">
-        <v>12576.22</v>
+        <v>15028.34</v>
       </c>
       <c r="G8" t="n">
-        <v>12701.36</v>
+        <v>15310.24</v>
       </c>
       <c r="H8" t="n">
-        <v>12644</v>
+        <v>15288.25</v>
       </c>
       <c r="I8" t="n">
-        <v>12457.37</v>
+        <v>15260.81</v>
       </c>
     </row>
     <row r="9">
@@ -694,28 +694,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1378720.069999996</v>
+        <v>1737044.209999998</v>
       </c>
       <c r="C9" t="n">
-        <v>1362777.650000002</v>
+        <v>1765100.920000001</v>
       </c>
       <c r="D9" t="n">
-        <v>1361544.599999999</v>
+        <v>1674785.810000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1445744.96</v>
+        <v>1601331.27</v>
       </c>
       <c r="F9" t="n">
-        <v>1544634.289999998</v>
+        <v>1719702.240000001</v>
       </c>
       <c r="G9" t="n">
-        <v>1461846.640000001</v>
+        <v>1870246.279999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1413893.9</v>
+        <v>1749342.740000002</v>
       </c>
       <c r="I9" t="n">
-        <v>1457271.569999997</v>
+        <v>1424746.669999999</v>
       </c>
     </row>
     <row r="10">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10345.54</v>
+        <v>15807.03</v>
       </c>
       <c r="C10" t="n">
-        <v>10764.14</v>
+        <v>17545.17</v>
       </c>
       <c r="D10" t="n">
-        <v>9611.279999999995</v>
+        <v>12828.79</v>
       </c>
       <c r="E10" t="n">
-        <v>8216.84</v>
+        <v>10437.25</v>
       </c>
       <c r="F10" t="n">
-        <v>10698.95</v>
+        <v>8861.760000000002</v>
       </c>
       <c r="G10" t="n">
-        <v>10196.72000000001</v>
+        <v>11689.72</v>
       </c>
       <c r="H10" t="n">
-        <v>11209.40999999999</v>
+        <v>10944.22</v>
       </c>
       <c r="I10" t="n">
-        <v>10664.34</v>
+        <v>11013.44</v>
       </c>
     </row>
     <row r="11">
@@ -756,28 +756,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35022.91000000001</v>
+        <v>281156.6199999999</v>
       </c>
       <c r="C11" t="n">
-        <v>33172.77000000001</v>
+        <v>895442.2499999997</v>
       </c>
       <c r="D11" t="n">
-        <v>32815.35999999999</v>
+        <v>894285.2999999997</v>
       </c>
       <c r="E11" t="n">
-        <v>29344.50999999999</v>
+        <v>832099.8700000003</v>
       </c>
       <c r="F11" t="n">
-        <v>35209.00000000001</v>
+        <v>825455.5899999997</v>
       </c>
       <c r="G11" t="n">
-        <v>32545.99999999999</v>
+        <v>29291.23</v>
       </c>
       <c r="H11" t="n">
-        <v>35247.49000000002</v>
+        <v>41564.41000000003</v>
       </c>
       <c r="I11" t="n">
-        <v>31165.14999999999</v>
+        <v>69323.54000000002</v>
       </c>
     </row>
     <row r="12">
@@ -787,31 +787,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>729122.6999999996</v>
+        <v>693741.0500000002</v>
       </c>
       <c r="C12" t="n">
-        <v>701875.6600000004</v>
+        <v>694637.3999999998</v>
       </c>
       <c r="D12" t="n">
-        <v>714332.6699999999</v>
+        <v>672878.2099999997</v>
       </c>
       <c r="E12" t="n">
-        <v>743788.97</v>
+        <v>692944.1299999998</v>
       </c>
       <c r="F12" t="n">
-        <v>726909.91</v>
+        <v>728571.0600000002</v>
       </c>
       <c r="G12" t="n">
-        <v>695111.05</v>
+        <v>680141.3200000002</v>
       </c>
       <c r="H12" t="n">
-        <v>705491.62</v>
+        <v>662543.9399999994</v>
       </c>
       <c r="I12" t="n">
-        <v>727275.5199999989</v>
+        <v>664833.7199999994</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>